--- a/etf_holdings/2026-10-20_daily_changes_changed_only.xlsx
+++ b/etf_holdings/2026-10-20_daily_changes_changed_only.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,70 +486,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>持續持有</t>
+          <t>新增</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>加碼</t>
+          <t>新納入</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1560</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>中砂</t>
-        </is>
-      </c>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>中砂</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0.20%</t>
-        </is>
-      </c>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.27%</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
-        <v>300000</v>
-      </c>
+          <t>0.33%</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>400000</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>100,000</t>
-        </is>
-      </c>
+        <v>4703000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-10-19_00403A_full_holdings.xlsx</t>
+          <t>2026-10-19_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -564,55 +546,55 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>2330</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>台積電</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.57%</t>
+          <t>10.86%</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>11.30%</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>75000</v>
+        <v>12392000</v>
       </c>
       <c r="K3" t="n">
-        <v>90000</v>
+        <v>12671000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>279,000</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-10-19_00403A_full_holdings.xlsx</t>
+          <t>2026-10-19_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -622,60 +604,60 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.61%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.51%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>15000000</v>
+        <v>5151450</v>
       </c>
       <c r="K4" t="n">
-        <v>10000000</v>
+        <v>6351450</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-5,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-10-19_00403A_full_holdings.xlsx</t>
+          <t>2026-10-19_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -705,40 +687,40 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>5.42%</t>
+          <t>7.58%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.68%</t>
+          <t>7.82%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>+0.26%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2140000</v>
+        <v>6303000</v>
       </c>
       <c r="K5" t="n">
-        <v>2200000</v>
+        <v>6343000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>60,000</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-10-19_00403A_full_holdings.xlsx</t>
+          <t>2026-10-19_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00403A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -753,55 +735,55 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>5.95%</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>6.19%</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>+0.33%</t>
+          <t>+0.24%</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>1697956</v>
+        <v>2502000</v>
       </c>
       <c r="K6" t="n">
-        <v>1850956</v>
+        <v>2512000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>153,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-10-19_00403A_full_holdings.xlsx</t>
+          <t>2026-10-19_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00981A</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -811,60 +793,60 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1216</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>統一</t>
+          <t>富世達</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>0.65%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.16%</t>
+          <t>0.70%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.45%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14442000</v>
+        <v>769000</v>
       </c>
       <c r="K7" t="n">
-        <v>11728000</v>
+        <v>819000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-2,714,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00981A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -879,55 +861,55 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>台達電</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>7.08%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>+7.10%</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>340000</v>
+        <v>470000</v>
       </c>
       <c r="K8" t="n">
-        <v>462000</v>
+        <v>482000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>122,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00991A</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -942,55 +924,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+1.51%</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>770000</v>
+        <v>150000</v>
       </c>
       <c r="K9" t="n">
-        <v>999000</v>
+        <v>170000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>229,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00991A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,55 +987,55 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>1.79%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.82%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>+1.13%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>156000</v>
+        <v>3216000</v>
       </c>
       <c r="K10" t="n">
-        <v>2294000</v>
+        <v>3234000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2,138,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1068,55 +1050,55 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>1.43%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>1.44%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>+0.39%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>378000</v>
+        <v>5116000</v>
       </c>
       <c r="K11" t="n">
-        <v>403000</v>
+        <v>5153000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>37,000</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1131,55 +1113,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>3.56%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.87%</t>
+          <t>3.63%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>+0.22%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>163000</v>
+        <v>845000</v>
       </c>
       <c r="K12" t="n">
-        <v>165000</v>
+        <v>851000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>6,000</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1189,60 +1171,60 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>236000</v>
+        <v>1737000</v>
       </c>
       <c r="K13" t="n">
-        <v>227000</v>
+        <v>1751000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-9,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1257,55 +1239,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3189</t>
+          <t>2428</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>景碩</t>
+          <t>興勤</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>+0.50%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1000</v>
+        <v>2268000</v>
       </c>
       <c r="K14" t="n">
-        <v>149000</v>
+        <v>2287000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>148,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1315,60 +1297,60 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2454</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>聯發科</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>6.59%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>7.03%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>+0.44%</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>9139000</v>
+        <v>736000</v>
       </c>
       <c r="K15" t="n">
-        <v>7183000</v>
+        <v>786000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-1,956,000</t>
+          <t>50,000</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,55 +1365,55 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.59%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>+1.18%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J16" t="n">
-        <v>227036</v>
+        <v>1529000</v>
       </c>
       <c r="K16" t="n">
-        <v>392036</v>
+        <v>1539000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>165,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00985A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1446,280 +1428,370 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>鉅祥</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>0.33%</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>160000</v>
+        <v>1281000</v>
       </c>
       <c r="K17" t="n">
-        <v>168000</v>
+        <v>1291000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>8,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2478</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>京元電子</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
+          <t>大毅</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>大毅</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.80%</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.13%</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-0.08%</t>
+        </is>
+      </c>
       <c r="J18" t="n">
-        <v>967000</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+        <v>4331000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4364000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>33,000</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>2026-10-19_00990A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IBIDEN CO LTD</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
+          <t>大立光</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>大立光</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1.42%</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
+          <t>3.38%</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>3.36%</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
       <c r="J19" t="n">
-        <v>236200</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+        <v>251000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>253000</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>2026-10-19_00990A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00990A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.61%</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+          <t>2.60%</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2.64%</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>+0.04%</t>
+        </is>
+      </c>
       <c r="J20" t="n">
-        <v>364000</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+        <v>372000</v>
+      </c>
+      <c r="K20" t="n">
+        <v>374000</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2026-10-19_00990A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>新增</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>新納入</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2313</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
+          <t>3265</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>台星科</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>華通</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
+          <t>台星科</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.47%</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>1.80%</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-0.09%</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>3345000</v>
+      </c>
       <c r="K21" t="n">
-        <v>400000</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
+        <v>3364000</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>19,000</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>2026-10-19_00407A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5289</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>宜鼎</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
+          <t>碩天</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>碩天</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.30%</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>0.35%</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
       <c r="J22" t="n">
-        <v>55294</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+        <v>627000</v>
+      </c>
+      <c r="K22" t="n">
+        <v>632000</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>2026-10-19_00407A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1734,55 +1806,55 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>+0.34%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>878000</v>
+        <v>876000</v>
       </c>
       <c r="K23" t="n">
-        <v>1198000</v>
+        <v>883000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>320,000</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2026-10-19_00407A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00407A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1792,105 +1864,123 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>減碼</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>台半</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2.82%</t>
+          <t>1.24%</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2.22%</t>
+          <t>1.25%</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-0.60%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>114000</v>
+        <v>6382000</v>
       </c>
       <c r="K24" t="n">
-        <v>94000</v>
+        <v>6406000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-20,000</t>
+          <t>24,000</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>2026-10-19_00407A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>刪除</t>
+          <t>持續持有</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>全數賣出</t>
+          <t>加碼</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>精材</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
+          <t>中美晶</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>中美晶</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.14%</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
+          <t>1.44%</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>-0.02%</t>
+        </is>
+      </c>
       <c r="J25" t="n">
-        <v>100000</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+        <v>3415000</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3439000</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>24,000</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1905,55 +1995,55 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>6196</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>川湖</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3.79%</t>
+          <t>0.39%</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>92000</v>
+        <v>304000</v>
       </c>
       <c r="K26" t="n">
-        <v>112000</v>
+        <v>306000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1968,55 +2058,55 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2330</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>台積電</t>
+          <t>聯茂</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>8.71%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>9.11%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>+0.40%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>1094000</v>
+        <v>940000</v>
       </c>
       <c r="K27" t="n">
-        <v>1131000</v>
+        <v>942000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>37,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2031,55 +2121,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>+0.97%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="J28" t="n">
-        <v>104000</v>
+        <v>418000</v>
       </c>
       <c r="K28" t="n">
-        <v>252000</v>
+        <v>421000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>148,000</t>
+          <t>3,000</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2094,55 +2184,55 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2454</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>聯發科</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>7.15%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>0.00%</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>445000</v>
+        <v>1082000</v>
       </c>
       <c r="K29" t="n">
-        <v>514000</v>
+        <v>1091000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>9,000</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00400A</t>
+          <t>00982A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2157,109 +2247,1702 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>騰輝電子-KY</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>+1.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="J30" t="n">
-        <v>1830000</v>
+        <v>1173000</v>
       </c>
       <c r="K30" t="n">
-        <v>2843000</v>
+        <v>1175000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1,013,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>00982A</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>長華*</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>長華*</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0.00%</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>4312000</v>
+      </c>
+      <c r="K31" t="n">
+        <v>4343000</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>31,000</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>2026-10-19_00982A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1216</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>統一</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3.61%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>3.16%</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>14442000</v>
+      </c>
+      <c r="K32" t="n">
+        <v>11728000</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-2,714,000</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2308</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>台達電</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2.57%</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>+0.82%</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>340000</v>
+      </c>
+      <c r="K33" t="n">
+        <v>462000</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>122,000</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2327</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>國巨*</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1.37%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>1.81%</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>+0.44%</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>770000</v>
+      </c>
+      <c r="K34" t="n">
+        <v>999000</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>229,000</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2344</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>華邦電</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0.08%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>1.21%</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>+1.13%</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>156000</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2294000</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2,138,000</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2.35%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>+0.39%</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>378000</v>
+      </c>
+      <c r="K36" t="n">
+        <v>403000</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>25,000</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2.65%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2.87%</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>+0.22%</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>163000</v>
+      </c>
+      <c r="K37" t="n">
+        <v>165000</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3081</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>聯亞</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1.89%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1.98%</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>+0.09%</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>236000</v>
+      </c>
+      <c r="K38" t="n">
+        <v>227000</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-9,000</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>3189</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>景碩</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>0.50%</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>+0.50%</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K39" t="n">
+        <v>149000</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>148,000</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4904</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>遠傳</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>3.26%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>-0.52%</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>9139000</v>
+      </c>
+      <c r="K40" t="n">
+        <v>7183000</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-1,956,000</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1.32%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>+1.18%</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>227036</v>
+      </c>
+      <c r="K41" t="n">
+        <v>392036</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>165,000</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>00985A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>7769</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>鴻勁</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2.66%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3.07%</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>+0.41%</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>160000</v>
+      </c>
+      <c r="K42" t="n">
+        <v>168000</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>8,000</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>2026-10-19_00985A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2383</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>台光電</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>5.16%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4.71%</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>-0.45%</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>475000</v>
+      </c>
+      <c r="K43" t="n">
+        <v>420000</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>-55,000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>2026-10-19_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>00992A</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2.76%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>1.75%</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>-1.01%</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>7185000</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4454000</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>-2,731,000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2026-10-19_00992A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>京元電子</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>0.80%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>967000</v>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>2026-10-19_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>4062</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>IBIDEN CO LTD</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1.42%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>236200</v>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>2026-10-19_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>00990A</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>臻鼎-KY</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.61%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>364000</v>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-10-19_00990A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>新納入</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2313</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>華通</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.47%</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="n">
+        <v>400000</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-10-19_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>5289</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>宜鼎</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="n">
+        <v>55294</v>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-10-19_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>1.09%</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>+0.34%</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>878000</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1198000</v>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>320,000</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-10-19_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>00407A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>6223</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>旺矽</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2.82%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2.22%</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>-0.60%</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>114000</v>
+      </c>
+      <c r="K51" t="n">
+        <v>94000</v>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>-20,000</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-10-19_00407A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>00400A</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>刪除</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>全數賣出</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>精材</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.14%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>100000</v>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>川湖</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>3.00%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3.79%</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>+0.79%</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>92000</v>
+      </c>
+      <c r="K53" t="n">
+        <v>112000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>8.71%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>9.11%</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>+0.40%</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1094000</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1131000</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>37,000</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0.69%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1.66%</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>+0.97%</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>104000</v>
+      </c>
+      <c r="K55" t="n">
+        <v>252000</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>148,000</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>6.16%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>7.15%</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>+0.99%</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>445000</v>
+      </c>
+      <c r="K56" t="n">
+        <v>514000</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>69,000</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>6278</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>台表科</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1.74%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2.74%</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>+1.00%</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1830000</v>
+      </c>
+      <c r="K57" t="n">
+        <v>2843000</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>1,013,000</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10-19_00400A_full_holdings.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>00400A</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D58" t="inlineStr">
         <is>
           <t>6505</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>台塑化</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>台塑化</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>2.35%</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>1.54%</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>-0.81%</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J58" t="n">
         <v>6147000</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K58" t="n">
         <v>4327000</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-1,820,000</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>2026-10-19_00400A_full_holdings.xlsx</t>
         </is>
